--- a/data/MARMR (TRY).xlsx
+++ b/data/MARMR (TRY).xlsx
@@ -12,6 +12,28 @@
     <sheet name="Nakit Akış (Yıllıklan.)" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -381,13 +403,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E108"/>
+  <dimension ref="A1:G108"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
     <col min="5" max="5" customWidth="1" width="20"/>
+    <col min="6" max="6" customWidth="1" width="20"/>
+    <col min="7" max="7" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -395,15 +419,21 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
+        <v>2024/12</v>
+      </c>
+      <c r="F1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>2024/6</v>
       </c>
     </row>
@@ -416,6 +446,12 @@
       <c r="A3" t="str">
         <v xml:space="preserve">    Nakit ve Nakit Benzerleri</v>
       </c>
+      <c r="B3">
+        <v>3464288</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -507,7 +543,13 @@
         <v xml:space="preserve">    Diğer Dönen Varlıklar</v>
       </c>
       <c r="B21">
-        <v>23441</v>
+        <v>288915</v>
+      </c>
+      <c r="C21">
+        <v>24461.908241813722</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -525,7 +567,13 @@
         <v xml:space="preserve">    Toplam Dönen Varlıklar</v>
       </c>
       <c r="B24">
-        <v>23441</v>
+        <v>3753203</v>
+      </c>
+      <c r="C24">
+        <v>24461.908241813722</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -583,7 +631,13 @@
         <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımlar</v>
       </c>
       <c r="B35">
-        <v>4515336171</v>
+        <v>4326312436</v>
+      </c>
+      <c r="C35">
+        <v>4711989211.038117</v>
+      </c>
+      <c r="E35">
+        <v>4757475556</v>
       </c>
     </row>
     <row r="36">
@@ -605,6 +659,12 @@
       <c r="A39" t="str">
         <v xml:space="preserve">    Maddi Duran Varlıklar</v>
       </c>
+      <c r="B39">
+        <v>11112</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -615,19 +675,31 @@
       <c r="A41" t="str">
         <v xml:space="preserve">    Maddi Olmayan Duran Varlıklar</v>
       </c>
-      <c r="B41">
-        <v>4030373</v>
+      <c r="C41">
+        <v>4205904.803817392</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
+      <c r="B42">
+        <v>526809</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
         <v xml:space="preserve">    Ertelenmiş Vergi Varlığı</v>
       </c>
+      <c r="B43">
+        <v>948323</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -649,7 +721,13 @@
         <v xml:space="preserve">    Toplam Duran Varlıklar</v>
       </c>
       <c r="B47">
-        <v>4519366544</v>
+        <v>4327798680</v>
+      </c>
+      <c r="C47">
+        <v>4716195115.841935</v>
+      </c>
+      <c r="E47">
+        <v>4757475556</v>
       </c>
     </row>
     <row r="48">
@@ -657,7 +735,13 @@
         <v xml:space="preserve">    Toplam Varlıklar</v>
       </c>
       <c r="B48">
-        <v>4519389985</v>
+        <v>4331551883</v>
+      </c>
+      <c r="C48">
+        <v>4716219577.750176</v>
+      </c>
+      <c r="E48">
+        <v>4757475556</v>
       </c>
     </row>
     <row r="49">
@@ -680,7 +764,13 @@
         <v xml:space="preserve">    Ticari Borçlar</v>
       </c>
       <c r="B52">
-        <v>4793160</v>
+        <v>4676758</v>
+      </c>
+      <c r="C52">
+        <v>5001912.892296909</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -692,13 +782,25 @@
       <c r="A54" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
       </c>
+      <c r="B54">
+        <v>128988</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
         <v xml:space="preserve">    Diğer Borçlar</v>
       </c>
       <c r="B55">
-        <v>3709</v>
+        <v>6649949</v>
+      </c>
+      <c r="C55">
+        <v>3870.535287269617</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -756,7 +858,13 @@
         <v xml:space="preserve">    Toplam Kısa Vadeli Yükümlülükler</v>
       </c>
       <c r="B66">
-        <v>4796869</v>
+        <v>11455695</v>
+      </c>
+      <c r="C66">
+        <v>5005783.427584179</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -851,6 +959,9 @@
       <c r="B84">
         <v>0</v>
       </c>
+      <c r="C84">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
@@ -862,7 +973,13 @@
         <v xml:space="preserve">    Ana Ortaklığa Ait Özkaynaklar</v>
       </c>
       <c r="B86">
-        <v>4514593116</v>
+        <v>4320096188</v>
+      </c>
+      <c r="C86">
+        <v>4711213794.322593</v>
+      </c>
+      <c r="E86">
+        <v>4757475556</v>
       </c>
     </row>
     <row r="87">
@@ -881,16 +998,34 @@
       <c r="E87">
         <v>3016276170</v>
       </c>
+      <c r="F87">
+        <v>3016276170</v>
+      </c>
+      <c r="G87">
+        <v>3016276170</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
         <v xml:space="preserve">    Sermaye Düzeltme Farkları</v>
       </c>
+      <c r="B88">
+        <v>236211062</v>
+      </c>
       <c r="C88">
-        <v>226352884.34487915</v>
+        <v>131365607.3349825</v>
+      </c>
+      <c r="D88">
+        <v>367576668.600044</v>
       </c>
       <c r="E88">
-        <v>226352884.34487915</v>
+        <v>236211062</v>
+      </c>
+      <c r="F88">
+        <v>131365607.3349825</v>
+      </c>
+      <c r="G88">
+        <v>367576668.600044</v>
       </c>
     </row>
     <row r="89">
@@ -938,7 +1073,13 @@
         <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılmayacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
       </c>
       <c r="B97">
+        <v>553362318</v>
+      </c>
+      <c r="C97">
         <v>0</v>
+      </c>
+      <c r="E97">
+        <v>823459973</v>
       </c>
     </row>
     <row r="98">
@@ -946,7 +1087,13 @@
         <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
       </c>
       <c r="B98">
-        <v>-1717201</v>
+        <v>-35354284</v>
+      </c>
+      <c r="C98">
+        <v>-1791988.9635574748</v>
+      </c>
+      <c r="E98">
+        <v>-35796328</v>
       </c>
     </row>
     <row r="99">
@@ -973,13 +1120,25 @@
       <c r="A103" t="str">
         <v xml:space="preserve">    Geçmiş Yıllar Kar/Zararları</v>
       </c>
+      <c r="B103">
+        <v>3657499277</v>
+      </c>
+      <c r="E103">
+        <v>3657499277</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
         <v xml:space="preserve">    Dönem Net Kar/Zararı</v>
       </c>
       <c r="B104">
-        <v>-42645967</v>
+        <v>-167723757</v>
+      </c>
+      <c r="C104">
+        <v>-44503294.724517554</v>
+      </c>
+      <c r="E104">
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -992,7 +1151,13 @@
         <v xml:space="preserve">    Toplam Özkaynaklar</v>
       </c>
       <c r="B106">
-        <v>4514593116</v>
+        <v>4320096188</v>
+      </c>
+      <c r="C106">
+        <v>4711213794.322593</v>
+      </c>
+      <c r="E106">
+        <v>4757475556</v>
       </c>
     </row>
     <row r="107">
@@ -1000,7 +1165,13 @@
         <v xml:space="preserve">    Toplam Kaynaklar</v>
       </c>
       <c r="B107">
-        <v>4519389985</v>
+        <v>4331551883</v>
+      </c>
+      <c r="C107">
+        <v>4716219577.750176</v>
+      </c>
+      <c r="E107">
+        <v>4757475556</v>
       </c>
     </row>
     <row r="108">
@@ -1010,17 +1181,18 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G108"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:C50"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
+    <col min="3" max="3" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1028,6 +1200,9 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/9</v>
       </c>
     </row>
@@ -1068,6 +1243,9 @@
       <c r="B8">
         <v>0</v>
       </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -1094,6 +1272,9 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
         <v>0</v>
       </c>
     </row>
@@ -1103,7 +1284,10 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-743055</v>
+        <v>-6684819</v>
+      </c>
+      <c r="C15">
+        <v>-775416.7155249731</v>
       </c>
     </row>
     <row r="16">
@@ -1120,11 +1304,17 @@
       <c r="A18" t="str">
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
+      <c r="B18">
+        <v>71994</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
+      <c r="B19">
+        <v>-163825</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -1136,7 +1326,10 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>-743055</v>
+        <v>-6776650</v>
+      </c>
+      <c r="C21">
+        <v>-775416.7155249731</v>
       </c>
     </row>
     <row r="22"/>
@@ -1154,6 +1347,9 @@
       <c r="A25" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
+      <c r="B25">
+        <v>12707</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -1170,7 +1366,10 @@
         <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımların Karlarından (Zararlarından) Paylar</v>
       </c>
       <c r="B28">
-        <v>-41902912</v>
+        <v>-161507509</v>
+      </c>
+      <c r="C28">
+        <v>-43727878.00899258</v>
       </c>
     </row>
     <row r="29">
@@ -1198,7 +1397,10 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>-42645967</v>
+        <v>-168271452</v>
+      </c>
+      <c r="C33">
+        <v>-44503294.724517554</v>
       </c>
     </row>
     <row r="34"/>
@@ -1206,23 +1408,35 @@
       <c r="A35" t="str">
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
+      <c r="B35">
+        <v>22246</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
+      <c r="B36">
+        <v>-548512</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
+      <c r="B37">
+        <v>125638</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>-42645967</v>
+        <v>-168672080</v>
+      </c>
+      <c r="C38">
+        <v>-44503294.724517554</v>
       </c>
     </row>
     <row r="39"/>
@@ -1230,6 +1444,9 @@
       <c r="A40" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
+      <c r="B40">
+        <v>948323</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -1240,13 +1457,19 @@
       <c r="A42" t="str">
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
+      <c r="B42">
+        <v>948323</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>-42645967</v>
+        <v>-167723757</v>
+      </c>
+      <c r="C43">
+        <v>-44503294.724517554</v>
       </c>
     </row>
     <row r="44">
@@ -1260,7 +1483,10 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>-42645967</v>
+        <v>-167723757</v>
+      </c>
+      <c r="C46">
+        <v>-44503294.724517554</v>
       </c>
     </row>
     <row r="47">
@@ -1270,13 +1496,19 @@
       <c r="B47">
         <v>0</v>
       </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>-42645967</v>
+        <v>-167723757</v>
+      </c>
+      <c r="C48">
+        <v>-44503294.724517554</v>
       </c>
     </row>
     <row r="49"/>
@@ -1284,23 +1516,24 @@
       <c r="A50" t="str">
         <v xml:space="preserve">    Amortisman</v>
       </c>
-      <c r="B50">
-        <v>711242</v>
+      <c r="C50">
+        <v>742218.1878641729</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:C50"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
+    <col min="3" max="3" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1308,6 +1541,9 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/9</v>
       </c>
     </row>
@@ -1345,6 +1581,9 @@
       <c r="A8" t="str">
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -1369,6 +1608,9 @@
     <row r="13">
       <c r="A13" t="str">
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
       </c>
     </row>
     <row r="14"/>
@@ -1376,6 +1618,9 @@
       <c r="A15" t="str">
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
+      <c r="B15">
+        <v>-5909402.284475027</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -1405,6 +1650,9 @@
     <row r="21">
       <c r="A21" t="str">
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
+      </c>
+      <c r="B21">
+        <v>-6001233.284475027</v>
       </c>
     </row>
     <row r="22"/>
@@ -1437,6 +1685,9 @@
       <c r="A28" t="str">
         <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımların Karlarından (Zararlarından) Paylar</v>
       </c>
+      <c r="B28">
+        <v>-117779630.99100742</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -1461,6 +1712,9 @@
     <row r="33">
       <c r="A33" t="str">
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
+      </c>
+      <c r="B33">
+        <v>-123768157.27548245</v>
       </c>
     </row>
     <row r="34"/>
@@ -1483,6 +1737,9 @@
       <c r="A38" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
+      <c r="B38">
+        <v>-124168785.27548245</v>
+      </c>
     </row>
     <row r="39"/>
     <row r="40">
@@ -1504,6 +1761,9 @@
       <c r="A43" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
+      <c r="B43">
+        <v>-123220462.27548245</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -1515,15 +1775,24 @@
       <c r="A46" t="str">
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
+      <c r="B46">
+        <v>-123220462.27548245</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
+      </c>
+      <c r="B48">
+        <v>-123220462.27548245</v>
       </c>
     </row>
     <row r="49"/>
@@ -1534,17 +1803,18 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:C50"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
+    <col min="3" max="3" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1552,6 +1822,9 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/9</v>
       </c>
     </row>
@@ -1589,6 +1862,9 @@
       <c r="A8" t="str">
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -1613,6 +1889,9 @@
     <row r="13">
       <c r="A13" t="str">
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
       </c>
     </row>
     <row r="14"/>
@@ -1620,6 +1899,9 @@
       <c r="A15" t="str">
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
+      <c r="B15">
+        <v>-6684819</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -1635,11 +1917,17 @@
       <c r="A18" t="str">
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
+      <c r="B18">
+        <v>71994</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
+      <c r="B19">
+        <v>-163825</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -1649,6 +1937,9 @@
     <row r="21">
       <c r="A21" t="str">
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
+      </c>
+      <c r="B21">
+        <v>-6776650</v>
       </c>
     </row>
     <row r="22"/>
@@ -1666,6 +1957,9 @@
       <c r="A25" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
+      <c r="B25">
+        <v>12707</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -1681,6 +1975,9 @@
       <c r="A28" t="str">
         <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımların Karlarından (Zararlarından) Paylar</v>
       </c>
+      <c r="B28">
+        <v>-161507509</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -1705,6 +2002,9 @@
     <row r="33">
       <c r="A33" t="str">
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
+      </c>
+      <c r="B33">
+        <v>-168271452</v>
       </c>
     </row>
     <row r="34"/>
@@ -1712,20 +2012,32 @@
       <c r="A35" t="str">
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
+      <c r="B35">
+        <v>22246</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
+      <c r="B36">
+        <v>-548512</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
+      <c r="B37">
+        <v>125638</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
+      </c>
+      <c r="B38">
+        <v>-168672080</v>
       </c>
     </row>
     <row r="39"/>
@@ -1733,6 +2045,9 @@
       <c r="A40" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
+      <c r="B40">
+        <v>948323</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -1743,10 +2058,16 @@
       <c r="A42" t="str">
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
+      <c r="B42">
+        <v>948323</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
+      </c>
+      <c r="B43">
+        <v>-167723757</v>
       </c>
     </row>
     <row r="44">
@@ -1759,15 +2080,24 @@
       <c r="A46" t="str">
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
+      <c r="B46">
+        <v>-167723757</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
+      </c>
+      <c r="B48">
+        <v>-167723757</v>
       </c>
     </row>
     <row r="49"/>
@@ -1778,17 +2108,18 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B130"/>
+  <dimension ref="A1:C129"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
+    <col min="3" max="3" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1796,6 +2127,9 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/9</v>
       </c>
     </row>
@@ -1809,6 +2143,9 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
+        <v>3440279</v>
+      </c>
+      <c r="C3">
         <v>0</v>
       </c>
     </row>
@@ -1817,7 +2154,10 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>-42645967</v>
+        <v>-167723757</v>
+      </c>
+      <c r="C4">
+        <v>-44503294.724517554</v>
       </c>
     </row>
     <row r="5">
@@ -1825,15 +2165,18 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>42614154</v>
+        <v>160524065</v>
+      </c>
+      <c r="C5">
+        <v>44470096.19685675</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
-      <c r="B6">
-        <v>711242</v>
+      <c r="C6">
+        <v>742218.1878641729</v>
       </c>
     </row>
     <row r="7">
@@ -1901,13 +2244,19 @@
         <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımların Dağıtılmamış Karları ile İlgili Düzeltmeler</v>
       </c>
       <c r="B19">
-        <v>41902912</v>
+        <v>161507509</v>
+      </c>
+      <c r="C19">
+        <v>43727878.00899258</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B20">
+        <v>-948323</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -1949,7 +2298,10 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>31813</v>
+        <v>10639971</v>
+      </c>
+      <c r="C28">
+        <v>33198.527660800304</v>
       </c>
     </row>
     <row r="29">
@@ -2006,13 +2358,19 @@
       <c r="A39" t="str">
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
+      <c r="B39">
+        <v>-526809</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>51545</v>
+        <v>4676758</v>
+      </c>
+      <c r="C40">
+        <v>53789.900615344406</v>
       </c>
     </row>
     <row r="41">
@@ -2024,6 +2382,9 @@
       <c r="A42" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
+      <c r="B42">
+        <v>128988</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -2035,7 +2396,10 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>3709</v>
+        <v>6649949</v>
+      </c>
+      <c r="C44">
+        <v>3870.535287269617</v>
       </c>
     </row>
     <row r="45">
@@ -2058,7 +2422,10 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>-23441</v>
+        <v>-288915</v>
+      </c>
+      <c r="C48">
+        <v>-24461.908241813722</v>
       </c>
     </row>
     <row r="49">
@@ -2066,6 +2433,9 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
+        <v>3440279</v>
+      </c>
+      <c r="C49">
         <v>0</v>
       </c>
     </row>
@@ -2141,362 +2511,379 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
-    <row r="67"/>
+    <row r="66"/>
+    <row r="67">
+      <c r="A67" t="str">
+        <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
+      </c>
+      <c r="B67">
+        <v>-11112</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+    </row>
     <row r="68">
       <c r="A68" t="str">
-        <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
-      </c>
-      <c r="B68">
-        <v>0</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğuracak Satışlara İlişkin Nakit Girişleri</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğuracak Satışlara İlişkin Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğurmayan Satışlara İlişkin Nakit Girişleri</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğurmayan Satışlara İlişkin Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Elde Edilmesine Yönelik Alışlara İlişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Elde Edilmesine Yönelik Alışlara İlişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
+        <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
+        <v xml:space="preserve">    İştirakler ve/veya İş Ortaklıkları Sermaye Avansı Ödemelerinden Nakit Çıkışları</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v xml:space="preserve">    İştirakler ve/veya İş Ortaklıkları Sermaye Avansı Ödemelerinden Nakit Çıkışları</v>
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
+      </c>
+      <c r="B78">
+        <v>-11112</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Satışlarından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Satışlarından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Alımlarından Nakit Çıkışları</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Alımlarından Nakit Çıkışları</v>
+        <v xml:space="preserve">    Canlı Varlık Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v xml:space="preserve">    Canlı Varlık Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Canlı Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v xml:space="preserve">    Canlı Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlar</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlar</v>
+        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlardan Geri Ödemeler</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlardan Geri Ödemeler</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Alınan Temettüler</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v xml:space="preserve">    Alınan Temettüler</v>
+        <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
+        <v xml:space="preserve">    Alınan Faiz</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
-    <row r="101"/>
+    <row r="100"/>
+    <row r="101">
+      <c r="A101" t="str">
+        <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
+      </c>
+      <c r="B101">
+        <v>0</v>
+      </c>
+      <c r="C101">
+        <v>0</v>
+      </c>
+    </row>
     <row r="102">
       <c r="A102" t="str">
-        <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
-      </c>
-      <c r="B102">
-        <v>0</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
+        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
+        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
+        <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Artış</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Artış</v>
+        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
+        <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Ödenen Temettüler</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v xml:space="preserve">    Ödenen Temettüler</v>
+        <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
+        <v xml:space="preserve">    Alınan Faiz</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
+        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
+        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+      </c>
+      <c r="B125">
+        <v>3429167</v>
+      </c>
+      <c r="C125">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
-      </c>
-      <c r="B126">
-        <v>0</v>
+        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
+        <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+      </c>
+      <c r="B127">
+        <v>3429167</v>
+      </c>
+      <c r="C127">
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+        <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
         <v>0</v>
       </c>
+      <c r="C128">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
+        <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="str">
-        <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
-      </c>
-      <c r="B130">
+        <v>3464288</v>
+      </c>
+      <c r="C129">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B130"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B130"/>
+  <dimension ref="A1:C129"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
+    <col min="3" max="3" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2504,6 +2891,9 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/9</v>
       </c>
     </row>
@@ -2516,16 +2906,25 @@
       <c r="A3" t="str">
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
+      <c r="B3">
+        <v>3440279</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
+      <c r="B4">
+        <v>-123220462.27548245</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B5">
+        <v>116053968.80314325</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -2596,6 +2995,9 @@
       <c r="A19" t="str">
         <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımların Dağıtılmamış Karları ile İlgili Düzeltmeler</v>
       </c>
+      <c r="B19">
+        <v>117779630.99100742</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -2641,6 +3043,9 @@
       <c r="A28" t="str">
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
+      <c r="B28">
+        <v>10606772.4723392</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -2701,6 +3106,9 @@
       <c r="A40" t="str">
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
+      <c r="B40">
+        <v>4622968.099384655</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -2721,6 +3129,9 @@
       <c r="A44" t="str">
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
+      <c r="B44">
+        <v>6646078.464712731</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
@@ -2741,11 +3152,17 @@
       <c r="A48" t="str">
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
+      <c r="B48">
+        <v>-264453.0917581863</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
+      <c r="B49">
+        <v>3440279</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -2819,344 +3236,358 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
-    <row r="67"/>
+    <row r="66"/>
+    <row r="67">
+      <c r="A67" t="str">
+        <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
+      </c>
+      <c r="B67">
+        <v>-11112</v>
+      </c>
+    </row>
     <row r="68">
       <c r="A68" t="str">
-        <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğuracak Satışlara İlişkin Nakit Girişleri</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğuracak Satışlara İlişkin Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğurmayan Satışlara İlişkin Nakit Girişleri</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğurmayan Satışlara İlişkin Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Elde Edilmesine Yönelik Alışlara İlişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Elde Edilmesine Yönelik Alışlara İlişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
+        <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
+        <v xml:space="preserve">    İştirakler ve/veya İş Ortaklıkları Sermaye Avansı Ödemelerinden Nakit Çıkışları</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v xml:space="preserve">    İştirakler ve/veya İş Ortaklıkları Sermaye Avansı Ödemelerinden Nakit Çıkışları</v>
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Satışlarından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Satışlarından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Alımlarından Nakit Çıkışları</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Alımlarından Nakit Çıkışları</v>
+        <v xml:space="preserve">    Canlı Varlık Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v xml:space="preserve">    Canlı Varlık Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Canlı Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v xml:space="preserve">    Canlı Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlar</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlar</v>
+        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlardan Geri Ödemeler</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlardan Geri Ödemeler</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Alınan Temettüler</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v xml:space="preserve">    Alınan Temettüler</v>
+        <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
+        <v xml:space="preserve">    Alınan Faiz</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
-    <row r="101"/>
+    <row r="100"/>
+    <row r="101">
+      <c r="A101" t="str">
+        <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
+      </c>
+      <c r="B101">
+        <v>0</v>
+      </c>
+    </row>
     <row r="102">
       <c r="A102" t="str">
-        <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
+        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
+        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
+        <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Artış</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Artış</v>
+        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
+        <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Ödenen Temettüler</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v xml:space="preserve">    Ödenen Temettüler</v>
+        <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
+        <v xml:space="preserve">    Alınan Faiz</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
+        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
+        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+      </c>
+      <c r="B125">
+        <v>3429167</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
+        <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+      </c>
+      <c r="B127">
+        <v>3429167</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+        <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
+      </c>
+      <c r="B128">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="str">
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
+      </c>
+      <c r="B129">
+        <v>3464288</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B130"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B130"/>
+  <dimension ref="A1:C129"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
+    <col min="3" max="3" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3164,6 +3595,9 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/9</v>
       </c>
     </row>
@@ -3176,16 +3610,25 @@
       <c r="A3" t="str">
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
+      <c r="B3">
+        <v>3440279</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
+      <c r="B4">
+        <v>-167723757</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B5">
+        <v>160524065</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -3256,11 +3699,17 @@
       <c r="A19" t="str">
         <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımların Dağıtılmamış Karları ile İlgili Düzeltmeler</v>
       </c>
+      <c r="B19">
+        <v>161507509</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B20">
+        <v>-948323</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -3301,6 +3750,9 @@
       <c r="A28" t="str">
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
+      <c r="B28">
+        <v>10639971</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -3356,11 +3808,17 @@
       <c r="A39" t="str">
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
+      <c r="B39">
+        <v>-526809</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
+      <c r="B40">
+        <v>4676758</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -3371,6 +3829,9 @@
       <c r="A42" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
+      <c r="B42">
+        <v>128988</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -3381,6 +3842,9 @@
       <c r="A44" t="str">
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
+      <c r="B44">
+        <v>6649949</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
@@ -3401,11 +3865,17 @@
       <c r="A48" t="str">
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
+      <c r="B48">
+        <v>-288915</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
+      <c r="B49">
+        <v>3440279</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -3479,334 +3949,350 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
-    <row r="67"/>
+    <row r="66"/>
+    <row r="67">
+      <c r="A67" t="str">
+        <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
+      </c>
+      <c r="B67">
+        <v>-11112</v>
+      </c>
+    </row>
     <row r="68">
       <c r="A68" t="str">
-        <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğuracak Satışlara İlişkin Nakit Girişleri</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğuracak Satışlara İlişkin Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğurmayan Satışlara İlişkin Nakit Girişleri</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğurmayan Satışlara İlişkin Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Elde Edilmesine Yönelik Alışlara İlişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Elde Edilmesine Yönelik Alışlara İlişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
+        <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
+        <v xml:space="preserve">    İştirakler ve/veya İş Ortaklıkları Sermaye Avansı Ödemelerinden Nakit Çıkışları</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v xml:space="preserve">    İştirakler ve/veya İş Ortaklıkları Sermaye Avansı Ödemelerinden Nakit Çıkışları</v>
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
+      </c>
+      <c r="B78">
+        <v>-11112</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Satışlarından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Satışlarından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Alımlarından Nakit Çıkışları</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Alımlarından Nakit Çıkışları</v>
+        <v xml:space="preserve">    Canlı Varlık Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v xml:space="preserve">    Canlı Varlık Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Canlı Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v xml:space="preserve">    Canlı Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlar</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlar</v>
+        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlardan Geri Ödemeler</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlardan Geri Ödemeler</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Alınan Temettüler</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v xml:space="preserve">    Alınan Temettüler</v>
+        <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
+        <v xml:space="preserve">    Alınan Faiz</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
-    <row r="101"/>
+    <row r="100"/>
+    <row r="101">
+      <c r="A101" t="str">
+        <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
+      </c>
+      <c r="B101">
+        <v>0</v>
+      </c>
+    </row>
     <row r="102">
       <c r="A102" t="str">
-        <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
+        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
+        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
+        <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Artış</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Artış</v>
+        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
+        <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Ödenen Temettüler</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v xml:space="preserve">    Ödenen Temettüler</v>
+        <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
+        <v xml:space="preserve">    Alınan Faiz</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
+        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
+        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+      </c>
+      <c r="B125">
+        <v>3429167</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
+        <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+      </c>
+      <c r="B127">
+        <v>3429167</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+        <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
+      </c>
+      <c r="B128">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="str">
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
+      </c>
+      <c r="B129">
+        <v>3464288</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B130"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C129"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/MARMR (TRY).xlsx
+++ b/data/MARMR (TRY).xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:H108"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -412,6 +412,7 @@
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -419,21 +420,24 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2024/6</v>
       </c>
     </row>
@@ -447,9 +451,12 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B3">
-        <v>3464288</v>
-      </c>
-      <c r="E3">
+        <v>2416774</v>
+      </c>
+      <c r="C3">
+        <v>3812178.8743237513</v>
+      </c>
+      <c r="F3">
         <v>0</v>
       </c>
     </row>
@@ -543,12 +550,15 @@
         <v xml:space="preserve">    Diğer Dönen Varlıklar</v>
       </c>
       <c r="B21">
-        <v>288915</v>
+        <v>1093852</v>
       </c>
       <c r="C21">
-        <v>24461.908241813722</v>
-      </c>
-      <c r="E21">
+        <v>317928.4342050218</v>
+      </c>
+      <c r="D21">
+        <v>26918.423013643303</v>
+      </c>
+      <c r="F21">
         <v>0</v>
       </c>
     </row>
@@ -567,12 +577,15 @@
         <v xml:space="preserve">    Toplam Dönen Varlıklar</v>
       </c>
       <c r="B24">
-        <v>3753203</v>
+        <v>3510626</v>
       </c>
       <c r="C24">
-        <v>24461.908241813722</v>
-      </c>
-      <c r="E24">
+        <v>4130107.308528773</v>
+      </c>
+      <c r="D24">
+        <v>26918.423013643303</v>
+      </c>
+      <c r="F24">
         <v>0</v>
       </c>
     </row>
@@ -631,13 +644,16 @@
         <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımlar</v>
       </c>
       <c r="B35">
-        <v>4326312436</v>
+        <v>4851255647</v>
       </c>
       <c r="C35">
-        <v>4711989211.038117</v>
-      </c>
-      <c r="E35">
-        <v>4757475556</v>
+        <v>4760769564.263515</v>
+      </c>
+      <c r="D35">
+        <v>5185176788.523631</v>
+      </c>
+      <c r="F35">
+        <v>5235230965.120349</v>
       </c>
     </row>
     <row r="36">
@@ -660,9 +676,12 @@
         <v xml:space="preserve">    Maddi Duran Varlıklar</v>
       </c>
       <c r="B39">
-        <v>11112</v>
-      </c>
-      <c r="E39">
+        <v>10701</v>
+      </c>
+      <c r="C39">
+        <v>12227.889728419093</v>
+      </c>
+      <c r="F39">
         <v>0</v>
       </c>
     </row>
@@ -675,8 +694,8 @@
       <c r="A41" t="str">
         <v xml:space="preserve">    Maddi Olmayan Duran Varlıklar</v>
       </c>
-      <c r="C41">
-        <v>4205904.803817392</v>
+      <c r="D41">
+        <v>4628270.351809504</v>
       </c>
     </row>
     <row r="42">
@@ -686,7 +705,10 @@
       <c r="B42">
         <v>526809</v>
       </c>
-      <c r="E42">
+      <c r="C42">
+        <v>579712.2354156529</v>
+      </c>
+      <c r="F42">
         <v>0</v>
       </c>
     </row>
@@ -697,7 +719,10 @@
       <c r="B43">
         <v>948323</v>
       </c>
-      <c r="E43">
+      <c r="C43">
+        <v>1043555.531940567</v>
+      </c>
+      <c r="F43">
         <v>0</v>
       </c>
     </row>
@@ -721,13 +746,16 @@
         <v xml:space="preserve">    Toplam Duran Varlıklar</v>
       </c>
       <c r="B47">
-        <v>4327798680</v>
+        <v>4852741480</v>
       </c>
       <c r="C47">
-        <v>4716195115.841935</v>
-      </c>
-      <c r="E47">
-        <v>4757475556</v>
+        <v>4762405059.9206</v>
+      </c>
+      <c r="D47">
+        <v>5189805058.875441</v>
+      </c>
+      <c r="F47">
+        <v>5235230965.120349</v>
       </c>
     </row>
     <row r="48">
@@ -735,13 +763,16 @@
         <v xml:space="preserve">    Toplam Varlıklar</v>
       </c>
       <c r="B48">
-        <v>4331551883</v>
+        <v>4856252106</v>
       </c>
       <c r="C48">
-        <v>4716219577.750176</v>
-      </c>
-      <c r="E48">
-        <v>4757475556</v>
+        <v>4766535167.229129</v>
+      </c>
+      <c r="D48">
+        <v>5189831977.298453</v>
+      </c>
+      <c r="F48">
+        <v>5235230965.120349</v>
       </c>
     </row>
     <row r="49">
@@ -764,12 +795,15 @@
         <v xml:space="preserve">    Ticari Borçlar</v>
       </c>
       <c r="B52">
-        <v>4676758</v>
+        <v>6608660</v>
       </c>
       <c r="C52">
-        <v>5001912.892296909</v>
-      </c>
-      <c r="E52">
+        <v>5146407.587338177</v>
+      </c>
+      <c r="D52">
+        <v>5504215.197818972</v>
+      </c>
+      <c r="F52">
         <v>0</v>
       </c>
     </row>
@@ -783,9 +817,12 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
       </c>
       <c r="B54">
-        <v>128988</v>
-      </c>
-      <c r="E54">
+        <v>457487</v>
+      </c>
+      <c r="C54">
+        <v>141941.23832697282</v>
+      </c>
+      <c r="F54">
         <v>0</v>
       </c>
     </row>
@@ -794,12 +831,15 @@
         <v xml:space="preserve">    Diğer Borçlar</v>
       </c>
       <c r="B55">
-        <v>6649949</v>
+        <v>9218818</v>
       </c>
       <c r="C55">
-        <v>3870.535287269617</v>
-      </c>
-      <c r="E55">
+        <v>7317750.456408462</v>
+      </c>
+      <c r="D55">
+        <v>4259.222343654409</v>
+      </c>
+      <c r="F55">
         <v>0</v>
       </c>
     </row>
@@ -858,12 +898,15 @@
         <v xml:space="preserve">    Toplam Kısa Vadeli Yükümlülükler</v>
       </c>
       <c r="B66">
-        <v>11455695</v>
+        <v>16284965</v>
       </c>
       <c r="C66">
-        <v>5005783.427584179</v>
-      </c>
-      <c r="E66">
+        <v>12606099.282073611</v>
+      </c>
+      <c r="D66">
+        <v>5508474.420162627</v>
+      </c>
+      <c r="F66">
         <v>0</v>
       </c>
     </row>
@@ -962,6 +1005,9 @@
       <c r="C84">
         <v>0</v>
       </c>
+      <c r="D84">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
@@ -973,13 +1019,16 @@
         <v xml:space="preserve">    Ana Ortaklığa Ait Özkaynaklar</v>
       </c>
       <c r="B86">
-        <v>4320096188</v>
+        <v>4839967141</v>
       </c>
       <c r="C86">
-        <v>4711213794.322593</v>
-      </c>
-      <c r="E86">
-        <v>4757475556</v>
+        <v>4753929067.947056</v>
+      </c>
+      <c r="D86">
+        <v>5184323502.878291</v>
+      </c>
+      <c r="F86">
+        <v>5235230965.120349</v>
       </c>
     </row>
     <row r="87">
@@ -1004,28 +1053,34 @@
       <c r="G87">
         <v>3016276170</v>
       </c>
+      <c r="H87">
+        <v>3016276170</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
         <v xml:space="preserve">    Sermaye Düzeltme Farkları</v>
       </c>
       <c r="B88">
-        <v>236211062</v>
+        <v>562832471</v>
       </c>
       <c r="C88">
-        <v>131365607.3349825</v>
+        <v>562832470.7475746</v>
       </c>
       <c r="D88">
-        <v>367576668.600044</v>
+        <v>447458221.4522365</v>
       </c>
       <c r="E88">
-        <v>236211062</v>
+        <v>707390079.7839516</v>
       </c>
       <c r="F88">
-        <v>131365607.3349825</v>
+        <v>562832470.7475746</v>
       </c>
       <c r="G88">
-        <v>367576668.600044</v>
+        <v>447458221.4522365</v>
+      </c>
+      <c r="H88">
+        <v>707390079.7839516</v>
       </c>
     </row>
     <row r="89">
@@ -1073,13 +1128,16 @@
         <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılmayacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
       </c>
       <c r="B97">
-        <v>553362318</v>
+        <v>599879920</v>
       </c>
       <c r="C97">
-        <v>0</v>
-      </c>
-      <c r="E97">
-        <v>823459973</v>
+        <v>608932091.8256282</v>
+      </c>
+      <c r="D97">
+        <v>0</v>
+      </c>
+      <c r="F97">
+        <v>906153504.8246008</v>
       </c>
     </row>
     <row r="98">
@@ -1087,13 +1145,16 @@
         <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
       </c>
       <c r="B98">
-        <v>-35354284</v>
+        <v>-42896228</v>
       </c>
       <c r="C98">
-        <v>-1791988.9635574748</v>
-      </c>
-      <c r="E98">
-        <v>-35796328</v>
+        <v>-38904633.3854582</v>
+      </c>
+      <c r="D98">
+        <v>-1971944.154150902</v>
+      </c>
+      <c r="F98">
+        <v>-39391068.34650115</v>
       </c>
     </row>
     <row r="99">
@@ -1121,10 +1182,13 @@
         <v xml:space="preserve">    Geçmiş Yıllar Kar/Zararları</v>
       </c>
       <c r="B103">
-        <v>3657499277</v>
-      </c>
-      <c r="E103">
-        <v>3657499277</v>
+        <v>3840225903</v>
+      </c>
+      <c r="C103">
+        <v>4024792822.2577896</v>
+      </c>
+      <c r="F103">
+        <v>4024792822.2577896</v>
       </c>
     </row>
     <row r="104">
@@ -1132,12 +1196,15 @@
         <v xml:space="preserve">    Dönem Net Kar/Zararı</v>
       </c>
       <c r="B104">
-        <v>-167723757</v>
+        <v>99081839</v>
       </c>
       <c r="C104">
-        <v>-44503294.724517554</v>
-      </c>
-      <c r="E104">
+        <v>-184566919.13536358</v>
+      </c>
+      <c r="D104">
+        <v>-48972406.44733044</v>
+      </c>
+      <c r="F104">
         <v>0</v>
       </c>
     </row>
@@ -1151,13 +1218,16 @@
         <v xml:space="preserve">    Toplam Özkaynaklar</v>
       </c>
       <c r="B106">
-        <v>4320096188</v>
+        <v>4839967141</v>
       </c>
       <c r="C106">
-        <v>4711213794.322593</v>
-      </c>
-      <c r="E106">
-        <v>4757475556</v>
+        <v>4753929067.947056</v>
+      </c>
+      <c r="D106">
+        <v>5184323502.878291</v>
+      </c>
+      <c r="F106">
+        <v>5235230965.120349</v>
       </c>
     </row>
     <row r="107">
@@ -1165,13 +1235,16 @@
         <v xml:space="preserve">    Toplam Kaynaklar</v>
       </c>
       <c r="B107">
-        <v>4331551883</v>
+        <v>4856252106</v>
       </c>
       <c r="C107">
-        <v>4716219577.750176</v>
-      </c>
-      <c r="E107">
-        <v>4757475556</v>
+        <v>4766535167.229129</v>
+      </c>
+      <c r="D107">
+        <v>5189831977.298453</v>
+      </c>
+      <c r="F107">
+        <v>5235230965.120349</v>
       </c>
     </row>
     <row r="108">
@@ -1181,18 +1254,20 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H108"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:E50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
+    <col min="4" max="4" customWidth="1" width="20"/>
+    <col min="5" max="5" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1200,10 +1275,16 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/9</v>
+      </c>
+      <c r="E1" t="str">
+        <v>2025/3</v>
       </c>
     </row>
     <row r="2">
@@ -1246,6 +1327,9 @@
       <c r="C8">
         <v>0</v>
       </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -1275,6 +1359,9 @@
         <v>0</v>
       </c>
       <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
         <v>0</v>
       </c>
     </row>
@@ -1284,10 +1371,13 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-6684819</v>
+        <v>-4882288</v>
       </c>
       <c r="C15">
-        <v>-775416.7155249731</v>
+        <v>-7356122.173005831</v>
+      </c>
+      <c r="D15">
+        <v>-853285.6453394789</v>
       </c>
     </row>
     <row r="16">
@@ -1305,7 +1395,10 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>71994</v>
+        <v>232677</v>
+      </c>
+      <c r="C18">
+        <v>79223.78447694423</v>
       </c>
     </row>
     <row r="19">
@@ -1313,7 +1406,10 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-163825</v>
+        <v>-35123</v>
+      </c>
+      <c r="C19">
+        <v>-180276.64099696346</v>
       </c>
     </row>
     <row r="20">
@@ -1326,10 +1422,13 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>-6776650</v>
+        <v>-4684734</v>
       </c>
       <c r="C21">
-        <v>-775416.7155249731</v>
+        <v>-7457175.02952585</v>
+      </c>
+      <c r="D21">
+        <v>-853285.6453394789</v>
       </c>
     </row>
     <row r="22"/>
@@ -1347,8 +1446,8 @@
       <c r="A25" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
-      <c r="B25">
-        <v>12707</v>
+      <c r="C25">
+        <v>13983.06288508112</v>
       </c>
     </row>
     <row r="26">
@@ -1366,10 +1465,13 @@
         <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımların Karlarından (Zararlarından) Paylar</v>
       </c>
       <c r="B28">
-        <v>-161507509</v>
+        <v>103529850</v>
       </c>
       <c r="C28">
-        <v>-43727878.00899258</v>
+        <v>-177726422.8189034</v>
+      </c>
+      <c r="D28">
+        <v>-48119120.80199096</v>
       </c>
     </row>
     <row r="29">
@@ -1391,16 +1493,22 @@
       <c r="A32" t="str">
         <v xml:space="preserve">    Risk Pozisyonlarını Netleştiren Kalemler Grubuna Yönelik Finansal Riskten Korunma Kazançları (Kayıpları)</v>
       </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>-168271452</v>
+        <v>98845116</v>
       </c>
       <c r="C33">
-        <v>-44503294.724517554</v>
+        <v>-185169614.78554416</v>
+      </c>
+      <c r="D33">
+        <v>-48972406.44733044</v>
       </c>
     </row>
     <row r="34"/>
@@ -1409,7 +1517,10 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
-        <v>22246</v>
+        <v>10737</v>
+      </c>
+      <c r="C35">
+        <v>24479.988741757665</v>
       </c>
     </row>
     <row r="36">
@@ -1417,7 +1528,10 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-548512</v>
+        <v>-513998</v>
+      </c>
+      <c r="C36">
+        <v>-603594.6949887162</v>
       </c>
     </row>
     <row r="37">
@@ -1425,7 +1539,10 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>125638</v>
+        <v>835217</v>
+      </c>
+      <c r="C37">
+        <v>138254.82448696168</v>
       </c>
     </row>
     <row r="38">
@@ -1433,10 +1550,13 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>-168672080</v>
+        <v>99177072</v>
       </c>
       <c r="C38">
-        <v>-44503294.724517554</v>
+        <v>-185610474.66730413</v>
+      </c>
+      <c r="D38">
+        <v>-48972406.44733044</v>
       </c>
     </row>
     <row r="39"/>
@@ -1445,7 +1565,10 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>948323</v>
+        <v>-95233</v>
+      </c>
+      <c r="C40">
+        <v>1043555.531940567</v>
       </c>
     </row>
     <row r="41">
@@ -1458,7 +1581,10 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>948323</v>
+        <v>-95233</v>
+      </c>
+      <c r="C42">
+        <v>1043555.531940567</v>
       </c>
     </row>
     <row r="43">
@@ -1466,10 +1592,13 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>-167723757</v>
+        <v>99081839</v>
       </c>
       <c r="C43">
-        <v>-44503294.724517554</v>
+        <v>-184566919.13536358</v>
+      </c>
+      <c r="D43">
+        <v>-48972406.44733044</v>
       </c>
     </row>
     <row r="44">
@@ -1483,10 +1612,13 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>-167723757</v>
+        <v>99081839</v>
       </c>
       <c r="C46">
-        <v>-44503294.724517554</v>
+        <v>-184566919.13536358</v>
+      </c>
+      <c r="D46">
+        <v>-48972406.44733044</v>
       </c>
     </row>
     <row r="47">
@@ -1499,16 +1631,22 @@
       <c r="C47">
         <v>0</v>
       </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>-167723757</v>
+        <v>99081839</v>
       </c>
       <c r="C48">
-        <v>-44503294.724517554</v>
+        <v>-184566919.13536358</v>
+      </c>
+      <c r="D48">
+        <v>-48972406.44733044</v>
       </c>
     </row>
     <row r="49"/>
@@ -1516,24 +1654,29 @@
       <c r="A50" t="str">
         <v xml:space="preserve">    Amortisman</v>
       </c>
-      <c r="C50">
-        <v>742218.1878641729</v>
+      <c r="B50">
+        <v>1527</v>
+      </c>
+      <c r="D50">
+        <v>816753.253746414</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:E50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
+    <col min="4" max="4" customWidth="1" width="20"/>
+    <col min="5" max="5" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1541,10 +1684,16 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/9</v>
+      </c>
+      <c r="E1" t="str">
+        <v>2025/3</v>
       </c>
     </row>
     <row r="2">
@@ -1584,6 +1733,9 @@
       <c r="B8">
         <v>0</v>
       </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -1610,6 +1762,9 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
         <v>0</v>
       </c>
     </row>
@@ -1619,7 +1774,10 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-5909402.284475027</v>
+        <v>-4882288</v>
+      </c>
+      <c r="C15">
+        <v>-6502836.527666353</v>
       </c>
     </row>
     <row r="16">
@@ -1636,11 +1794,17 @@
       <c r="A18" t="str">
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
+      <c r="B18">
+        <v>232677</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
+      <c r="B19">
+        <v>-35123</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -1652,7 +1816,10 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>-6001233.284475027</v>
+        <v>-4684734</v>
+      </c>
+      <c r="C21">
+        <v>-6603889.384186371</v>
       </c>
     </row>
     <row r="22"/>
@@ -1686,7 +1853,10 @@
         <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımların Karlarından (Zararlarından) Paylar</v>
       </c>
       <c r="B28">
-        <v>-117779630.99100742</v>
+        <v>103529850</v>
+      </c>
+      <c r="C28">
+        <v>-129607302.01691243</v>
       </c>
     </row>
     <row r="29">
@@ -1708,13 +1878,19 @@
       <c r="A32" t="str">
         <v xml:space="preserve">    Risk Pozisyonlarını Netleştiren Kalemler Grubuna Yönelik Finansal Riskten Korunma Kazançları (Kayıpları)</v>
       </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>-123768157.27548245</v>
+        <v>98845116</v>
+      </c>
+      <c r="C33">
+        <v>-136197208.3382137</v>
       </c>
     </row>
     <row r="34"/>
@@ -1722,23 +1898,35 @@
       <c r="A35" t="str">
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
+      <c r="B35">
+        <v>10737</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
+      <c r="B36">
+        <v>-513998</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
+      <c r="B37">
+        <v>835217</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>-124168785.27548245</v>
+        <v>99177072</v>
+      </c>
+      <c r="C38">
+        <v>-136638068.21997368</v>
       </c>
     </row>
     <row r="39"/>
@@ -1746,6 +1934,9 @@
       <c r="A40" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
+      <c r="B40">
+        <v>-95233</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -1756,13 +1947,19 @@
       <c r="A42" t="str">
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
+      <c r="B42">
+        <v>-95233</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>-123220462.27548245</v>
+        <v>99081839</v>
+      </c>
+      <c r="C43">
+        <v>-135594512.68803313</v>
       </c>
     </row>
     <row r="44">
@@ -1776,7 +1973,10 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>-123220462.27548245</v>
+        <v>99081839</v>
+      </c>
+      <c r="C46">
+        <v>-135594512.68803313</v>
       </c>
     </row>
     <row r="47">
@@ -1786,13 +1986,19 @@
       <c r="B47">
         <v>0</v>
       </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>-123220462.27548245</v>
+        <v>99081839</v>
+      </c>
+      <c r="C48">
+        <v>-135594512.68803313</v>
       </c>
     </row>
     <row r="49"/>
@@ -1800,21 +2006,26 @@
       <c r="A50" t="str">
         <v xml:space="preserve">    Amortisman</v>
       </c>
+      <c r="B50">
+        <v>1527</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:E50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
+    <col min="4" max="4" customWidth="1" width="20"/>
+    <col min="5" max="5" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1822,10 +2033,16 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/9</v>
+      </c>
+      <c r="E1" t="str">
+        <v>2025/3</v>
       </c>
     </row>
     <row r="2">
@@ -1862,7 +2079,7 @@
       <c r="A8" t="str">
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
-      <c r="B8">
+      <c r="C8">
         <v>0</v>
       </c>
     </row>
@@ -1890,7 +2107,7 @@
       <c r="A13" t="str">
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
-      <c r="B13">
+      <c r="C13">
         <v>0</v>
       </c>
     </row>
@@ -1899,8 +2116,8 @@
       <c r="A15" t="str">
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
-      <c r="B15">
-        <v>-6684819</v>
+      <c r="C15">
+        <v>-7356122.173005831</v>
       </c>
     </row>
     <row r="16">
@@ -1917,16 +2134,16 @@
       <c r="A18" t="str">
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
-      <c r="B18">
-        <v>71994</v>
+      <c r="C18">
+        <v>79223.78447694423</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
-      <c r="B19">
-        <v>-163825</v>
+      <c r="C19">
+        <v>-180276.64099696346</v>
       </c>
     </row>
     <row r="20">
@@ -1938,8 +2155,8 @@
       <c r="A21" t="str">
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
-      <c r="B21">
-        <v>-6776650</v>
+      <c r="C21">
+        <v>-7457175.02952585</v>
       </c>
     </row>
     <row r="22"/>
@@ -1957,8 +2174,8 @@
       <c r="A25" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
-      <c r="B25">
-        <v>12707</v>
+      <c r="C25">
+        <v>13983.06288508112</v>
       </c>
     </row>
     <row r="26">
@@ -1975,8 +2192,8 @@
       <c r="A28" t="str">
         <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımların Karlarından (Zararlarından) Paylar</v>
       </c>
-      <c r="B28">
-        <v>-161507509</v>
+      <c r="C28">
+        <v>-177726422.8189034</v>
       </c>
     </row>
     <row r="29">
@@ -2003,8 +2220,8 @@
       <c r="A33" t="str">
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
-      <c r="B33">
-        <v>-168271452</v>
+      <c r="C33">
+        <v>-185169614.78554416</v>
       </c>
     </row>
     <row r="34"/>
@@ -2012,32 +2229,32 @@
       <c r="A35" t="str">
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
-      <c r="B35">
-        <v>22246</v>
+      <c r="C35">
+        <v>24479.988741757665</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
-      <c r="B36">
-        <v>-548512</v>
+      <c r="C36">
+        <v>-603594.6949887162</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
-      <c r="B37">
-        <v>125638</v>
+      <c r="C37">
+        <v>138254.82448696168</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
-      <c r="B38">
-        <v>-168672080</v>
+      <c r="C38">
+        <v>-185610474.66730413</v>
       </c>
     </row>
     <row r="39"/>
@@ -2045,8 +2262,8 @@
       <c r="A40" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
-      <c r="B40">
-        <v>948323</v>
+      <c r="C40">
+        <v>1043555.531940567</v>
       </c>
     </row>
     <row r="41">
@@ -2058,16 +2275,16 @@
       <c r="A42" t="str">
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
-      <c r="B42">
-        <v>948323</v>
+      <c r="C42">
+        <v>1043555.531940567</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
-      <c r="B43">
-        <v>-167723757</v>
+      <c r="C43">
+        <v>-184566919.13536358</v>
       </c>
     </row>
     <row r="44">
@@ -2080,15 +2297,15 @@
       <c r="A46" t="str">
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
-      <c r="B46">
-        <v>-167723757</v>
+      <c r="C46">
+        <v>-184566919.13536358</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
-      <c r="B47">
+      <c r="C47">
         <v>0</v>
       </c>
     </row>
@@ -2096,8 +2313,8 @@
       <c r="A48" t="str">
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
-      <c r="B48">
-        <v>-167723757</v>
+      <c r="C48">
+        <v>-184566919.13536358</v>
       </c>
     </row>
     <row r="49"/>
@@ -2108,18 +2325,19 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C129"/>
+  <dimension ref="A1:D129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
+    <col min="4" max="4" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2127,9 +2345,12 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/9</v>
       </c>
     </row>
@@ -2143,9 +2364,12 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>3440279</v>
+        <v>-1047514</v>
       </c>
       <c r="C3">
+        <v>3785758.84152231</v>
+      </c>
+      <c r="D3">
         <v>0</v>
       </c>
     </row>
@@ -2154,10 +2378,13 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>-167723757</v>
+        <v>99081839</v>
       </c>
       <c r="C4">
-        <v>-44503294.724517554</v>
+        <v>-184566919.13536358</v>
+      </c>
+      <c r="D4">
+        <v>-48972406.44733044</v>
       </c>
     </row>
     <row r="5">
@@ -2165,18 +2392,24 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>160524065</v>
+        <v>-104153686</v>
       </c>
       <c r="C5">
-        <v>44470096.19685675</v>
+        <v>176644219.36443296</v>
+      </c>
+      <c r="D5">
+        <v>48935874.05573737</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
-      <c r="C6">
-        <v>742218.1878641729</v>
+      <c r="B6">
+        <v>1527</v>
+      </c>
+      <c r="D6">
+        <v>816753.253746414</v>
       </c>
     </row>
     <row r="7">
@@ -2244,10 +2477,13 @@
         <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımların Dağıtılmamış Karları ile İlgili Düzeltmeler</v>
       </c>
       <c r="B19">
-        <v>161507509</v>
+        <v>-103529850</v>
       </c>
       <c r="C19">
-        <v>43727878.00899258</v>
+        <v>177726422.8189034</v>
+      </c>
+      <c r="D19">
+        <v>48119120.80199096</v>
       </c>
     </row>
     <row r="20">
@@ -2255,7 +2491,10 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
-        <v>-948323</v>
+        <v>95233</v>
+      </c>
+      <c r="C20">
+        <v>-1043555.531940567</v>
       </c>
     </row>
     <row r="21">
@@ -2298,10 +2537,13 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>10639971</v>
+        <v>4024333</v>
       </c>
       <c r="C28">
-        <v>33198.527660800304</v>
+        <v>11708458.612452937</v>
+      </c>
+      <c r="D28">
+        <v>36532.3915930649</v>
       </c>
     </row>
     <row r="29">
@@ -2328,6 +2570,9 @@
       <c r="A33" t="str">
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
+      <c r="B33">
+        <v>-804937</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -2359,7 +2604,10 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>-526809</v>
+        <v>0</v>
+      </c>
+      <c r="C39">
+        <v>-579712.2354156529</v>
       </c>
     </row>
     <row r="40">
@@ -2367,10 +2615,13 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>4676758</v>
+        <v>1931902</v>
       </c>
       <c r="C40">
-        <v>53789.900615344406</v>
+        <v>5146407.587338177</v>
+      </c>
+      <c r="D40">
+        <v>59191.59226305379</v>
       </c>
     </row>
     <row r="41">
@@ -2383,7 +2634,10 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>128988</v>
+        <v>328499</v>
+      </c>
+      <c r="C42">
+        <v>141941.23832697282</v>
       </c>
     </row>
     <row r="43">
@@ -2396,10 +2650,13 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>6649949</v>
+        <v>2568869</v>
       </c>
       <c r="C44">
-        <v>3870.535287269617</v>
+        <v>7317750.456408462</v>
+      </c>
+      <c r="D44">
+        <v>4259.222343654409</v>
       </c>
     </row>
     <row r="45">
@@ -2421,11 +2678,11 @@
       <c r="A48" t="str">
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
-      <c r="B48">
-        <v>-288915</v>
-      </c>
       <c r="C48">
-        <v>-24461.908241813722</v>
+        <v>-317928.4342050218</v>
+      </c>
+      <c r="D48">
+        <v>-26918.423013643303</v>
       </c>
     </row>
     <row r="49">
@@ -2433,9 +2690,12 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>3440279</v>
+        <v>-1047514</v>
       </c>
       <c r="C49">
+        <v>3785758.84152231</v>
+      </c>
+      <c r="D49">
         <v>0</v>
       </c>
     </row>
@@ -2525,9 +2785,12 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
-        <v>-11112</v>
+        <v>0</v>
       </c>
       <c r="C67">
+        <v>-12227.889728419093</v>
+      </c>
+      <c r="D67">
         <v>0</v>
       </c>
     </row>
@@ -2585,8 +2848,8 @@
       <c r="A78" t="str">
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
-      <c r="B78">
-        <v>-11112</v>
+      <c r="C78">
+        <v>-12227.889728419093</v>
       </c>
     </row>
     <row r="79">
@@ -2705,6 +2968,9 @@
       <c r="C101">
         <v>0</v>
       </c>
+      <c r="D101">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
@@ -2826,9 +3092,12 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
-        <v>3429167</v>
+        <v>-1047514</v>
       </c>
       <c r="C125">
+        <v>3773530.951793891</v>
+      </c>
+      <c r="D125">
         <v>0</v>
       </c>
     </row>
@@ -2842,9 +3111,12 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>3429167</v>
+        <v>-1047514</v>
       </c>
       <c r="C127">
+        <v>3773530.951793891</v>
+      </c>
+      <c r="D127">
         <v>0</v>
       </c>
     </row>
@@ -2853,9 +3125,12 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>0</v>
+        <v>3812179</v>
       </c>
       <c r="C128">
+        <v>0</v>
+      </c>
+      <c r="D128">
         <v>0</v>
       </c>
     </row>
@@ -2864,26 +3139,30 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>3464288</v>
+        <v>2416774</v>
       </c>
       <c r="C129">
+        <v>3812178.8743237513</v>
+      </c>
+      <c r="D129">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C129"/>
+  <dimension ref="A1:D129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
+    <col min="4" max="4" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2891,9 +3170,12 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/9</v>
       </c>
     </row>
@@ -2907,7 +3189,10 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>3440279</v>
+        <v>-1047514</v>
+      </c>
+      <c r="C3">
+        <v>3785758.84152231</v>
       </c>
     </row>
     <row r="4">
@@ -2915,7 +3200,10 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>-123220462.27548245</v>
+        <v>99081839</v>
+      </c>
+      <c r="C4">
+        <v>-135594512.68803313</v>
       </c>
     </row>
     <row r="5">
@@ -2923,13 +3211,19 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>116053968.80314325</v>
+        <v>-104153686</v>
+      </c>
+      <c r="C5">
+        <v>127708345.30869558</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B6">
+        <v>1527</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -2996,13 +3290,19 @@
         <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımların Dağıtılmamış Karları ile İlgili Düzeltmeler</v>
       </c>
       <c r="B19">
-        <v>117779630.99100742</v>
+        <v>-103529850</v>
+      </c>
+      <c r="C19">
+        <v>129607302.01691243</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B20">
+        <v>95233</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -3044,7 +3344,10 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>10606772.4723392</v>
+        <v>4024333</v>
+      </c>
+      <c r="C28">
+        <v>11671926.220859872</v>
       </c>
     </row>
     <row r="29">
@@ -3071,6 +3374,9 @@
       <c r="A33" t="str">
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
+      <c r="B33">
+        <v>-804937</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -3101,13 +3407,19 @@
       <c r="A39" t="str">
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
+      <c r="B39">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>4622968.099384655</v>
+        <v>1931902</v>
+      </c>
+      <c r="C40">
+        <v>5087215.995075122</v>
       </c>
     </row>
     <row r="41">
@@ -3119,6 +3431,9 @@
       <c r="A42" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
+      <c r="B42">
+        <v>328499</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -3130,7 +3445,10 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>6646078.464712731</v>
+        <v>2568869</v>
+      </c>
+      <c r="C44">
+        <v>7313491.234064807</v>
       </c>
     </row>
     <row r="45">
@@ -3152,8 +3470,8 @@
       <c r="A48" t="str">
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
-      <c r="B48">
-        <v>-264453.0917581863</v>
+      <c r="C48">
+        <v>-291010.0111913785</v>
       </c>
     </row>
     <row r="49">
@@ -3161,7 +3479,10 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>3440279</v>
+        <v>-1047514</v>
+      </c>
+      <c r="C49">
+        <v>3785758.84152231</v>
       </c>
     </row>
     <row r="50">
@@ -3250,7 +3571,10 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
-        <v>-11112</v>
+        <v>0</v>
+      </c>
+      <c r="C67">
+        <v>-12227.889728419093</v>
       </c>
     </row>
     <row r="68">
@@ -3421,6 +3745,9 @@
       <c r="B101">
         <v>0</v>
       </c>
+      <c r="C101">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
@@ -3542,7 +3869,10 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
-        <v>3429167</v>
+        <v>-1047514</v>
+      </c>
+      <c r="C125">
+        <v>3773530.951793891</v>
       </c>
     </row>
     <row r="126">
@@ -3555,7 +3885,10 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>3429167</v>
+        <v>-1047514</v>
+      </c>
+      <c r="C127">
+        <v>3773530.951793891</v>
       </c>
     </row>
     <row r="128">
@@ -3563,6 +3896,9 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
+        <v>3812179</v>
+      </c>
+      <c r="C128">
         <v>0</v>
       </c>
     </row>
@@ -3571,23 +3907,27 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>3464288</v>
+        <v>2416774</v>
+      </c>
+      <c r="C129">
+        <v>3812178.8743237513</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C129"/>
+  <dimension ref="A1:D129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
+    <col min="4" max="4" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3595,9 +3935,12 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/9</v>
       </c>
     </row>
@@ -3610,24 +3953,24 @@
       <c r="A3" t="str">
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
-      <c r="B3">
-        <v>3440279</v>
+      <c r="C3">
+        <v>3785758.84152231</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
-      <c r="B4">
-        <v>-167723757</v>
+      <c r="C4">
+        <v>-184566919.13536358</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
-      <c r="B5">
-        <v>160524065</v>
+      <c r="C5">
+        <v>176644219.36443296</v>
       </c>
     </row>
     <row r="6">
@@ -3699,16 +4042,16 @@
       <c r="A19" t="str">
         <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımların Dağıtılmamış Karları ile İlgili Düzeltmeler</v>
       </c>
-      <c r="B19">
-        <v>161507509</v>
+      <c r="C19">
+        <v>177726422.8189034</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
-      <c r="B20">
-        <v>-948323</v>
+      <c r="C20">
+        <v>-1043555.531940567</v>
       </c>
     </row>
     <row r="21">
@@ -3750,8 +4093,8 @@
       <c r="A28" t="str">
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
-      <c r="B28">
-        <v>10639971</v>
+      <c r="C28">
+        <v>11708458.612452937</v>
       </c>
     </row>
     <row r="29">
@@ -3808,16 +4151,16 @@
       <c r="A39" t="str">
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
-      <c r="B39">
-        <v>-526809</v>
+      <c r="C39">
+        <v>-579712.2354156529</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
-      <c r="B40">
-        <v>4676758</v>
+      <c r="C40">
+        <v>5146407.587338177</v>
       </c>
     </row>
     <row r="41">
@@ -3829,8 +4172,8 @@
       <c r="A42" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
-      <c r="B42">
-        <v>128988</v>
+      <c r="C42">
+        <v>141941.23832697282</v>
       </c>
     </row>
     <row r="43">
@@ -3842,8 +4185,8 @@
       <c r="A44" t="str">
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
-      <c r="B44">
-        <v>6649949</v>
+      <c r="C44">
+        <v>7317750.456408462</v>
       </c>
     </row>
     <row r="45">
@@ -3865,16 +4208,16 @@
       <c r="A48" t="str">
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
-      <c r="B48">
-        <v>-288915</v>
+      <c r="C48">
+        <v>-317928.4342050218</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
-      <c r="B49">
-        <v>3440279</v>
+      <c r="C49">
+        <v>3785758.84152231</v>
       </c>
     </row>
     <row r="50">
@@ -3962,8 +4305,8 @@
       <c r="A67" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
-      <c r="B67">
-        <v>-11112</v>
+      <c r="C67">
+        <v>-12227.889728419093</v>
       </c>
     </row>
     <row r="68">
@@ -4020,8 +4363,8 @@
       <c r="A78" t="str">
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
-      <c r="B78">
-        <v>-11112</v>
+      <c r="C78">
+        <v>-12227.889728419093</v>
       </c>
     </row>
     <row r="79">
@@ -4134,7 +4477,7 @@
       <c r="A101" t="str">
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
-      <c r="B101">
+      <c r="C101">
         <v>0</v>
       </c>
     </row>
@@ -4257,8 +4600,8 @@
       <c r="A125" t="str">
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
-      <c r="B125">
-        <v>3429167</v>
+      <c r="C125">
+        <v>3773530.951793891</v>
       </c>
     </row>
     <row r="126">
@@ -4270,15 +4613,15 @@
       <c r="A127" t="str">
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
-      <c r="B127">
-        <v>3429167</v>
+      <c r="C127">
+        <v>3773530.951793891</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
-      <c r="B128">
+      <c r="C128">
         <v>0</v>
       </c>
     </row>
@@ -4286,13 +4629,13 @@
       <c r="A129" t="str">
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
-      <c r="B129">
-        <v>3464288</v>
+      <c r="C129">
+        <v>3812178.8743237513</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D129"/>
   </ignoredErrors>
 </worksheet>
 </file>